--- a/questionnaire_templates/046_vehicle_driver_questionnaire--questionnaire_templates.xlsx
+++ b/questionnaire_templates/046_vehicle_driver_questionnaire--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>vehicle_type</t>
+          <t>vehicle_type_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vehicle Type</t>
+          <t>Vehicle Type 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>vehicle_year</t>
+          <t>vehicle_year_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Vehicle Year</t>
+          <t>Vehicle Year 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>vehicle_type</t>
+          <t>vehicle_type_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Vehicle Type</t>
+          <t>Vehicle Type 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1330,7 +1330,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>vehicle_type_choices</t>
+          <t>vehicle_type_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,7 +1347,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>vehicle_type_choices</t>
+          <t>vehicle_type_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1466,7 +1466,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>vehicle_year_choices</t>
+          <t>vehicle_year_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>vehicle_year_choices</t>
+          <t>vehicle_year_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1500,7 +1500,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>vehicle_type_choices</t>
+          <t>vehicle_type_3_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1517,7 +1517,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>vehicle_type_choices</t>
+          <t>vehicle_type_3_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
